--- a/hall/resources/sample/CasinoList.xlsx
+++ b/hall/resources/sample/CasinoList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoList" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
-    <t>ID</t>
+    <t>场景ID</t>
   </si>
   <si>
     <t>名称</t>

--- a/hall/resources/sample/CasinoList.xlsx
+++ b/hall/resources/sample/CasinoList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoList" sheetId="1" r:id="rId1"/>
@@ -126,31 +126,31 @@
     <t>滨海湾金沙</t>
   </si>
   <si>
-    <t>1001_999</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>云顶赌场</t>
   </si>
   <si>
-    <t>1001_999;1002_999</t>
+    <t>2_10</t>
   </si>
   <si>
     <t>滨海赌场</t>
   </si>
   <si>
-    <t>1002_999;1003_999</t>
+    <t>3_10</t>
   </si>
   <si>
     <t>亚特兰蒂斯</t>
   </si>
   <si>
-    <t>1003_999;1004_999</t>
+    <t>4_10</t>
   </si>
   <si>
     <t>巴登赌场</t>
   </si>
   <si>
-    <t>1004_999;1005_999</t>
+    <t>4_20;5_10</t>
   </si>
 </sst>
 </file>
@@ -1140,8 +1140,9 @@
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="15.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="41.6083333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.8166666666667" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.625" style="2" customWidth="1"/>
     <col min="7" max="16384" width="15.625" style="2"/>
   </cols>

--- a/hall/resources/sample/CasinoList.xlsx
+++ b/hall/resources/sample/CasinoList.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoList" sheetId="1" r:id="rId1"/>
@@ -32,6 +37,29 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这个字段废弃；改完按已解锁的区域交互点的2倍进行统计；
+取2倍的原因是：一个交互点有一个等待点；</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E3" authorId="0">
       <text>
         <r>
@@ -163,7 +191,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +215,19 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2" tint="-0.1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -672,137 +713,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -818,10 +859,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1135,7 +1182,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -1163,7 +1210,7 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1179,7 +1226,7 @@
       <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1195,114 +1242,118 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:6">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" customHeight="1" spans="1:6">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>4011001</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="2">
-        <v>200</v>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7">
+        <v>80</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="2">
         <v>4011002</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="2">
-        <v>200</v>
+      <c r="F6" s="7">
+        <v>80</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>4011003</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="2">
-        <v>200</v>
+      <c r="F7" s="7">
+        <v>80</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:6">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="2">
         <v>4011004</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="2">
-        <v>200</v>
+      <c r="F8" s="7">
+        <v>80</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:6">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="2">
         <v>4011005</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="2">
-        <v>200</v>
+      <c r="F9" s="7">
+        <v>80</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:6">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="2">
         <v>4011006</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="2">
-        <v>200</v>
-      </c>
+      <c r="F10" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:6">
+      <c r="F11" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
